--- a/dict.xlsx
+++ b/dict.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cnrer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codex\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BF828C-8EE8-4D9F-92A8-BD7A88520134}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6926938-B48A-424E-9D80-1CD33C7117D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,6 +56,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> cold 中国有广袤的沙漠，从酷热难耐到寒冷刺骨。</t>
     </r>
@@ -538,6 +539,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>There is a 20-year waiting list, so you have to put your child on the list as soon as they are conceived (马斯克说的是东德的汽车）（用 There is 来引出存在的事实，更符合常见的句子结构，不用 that is）
 conceivable adj.可想到的，可相信的，可想象的。It is hardly conceivable that she should do such a thing.
@@ -1304,6 +1306,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> n.v. 畏惧，害怕。in dread of 在恐惧之中。she dreaded to going piano lessons。The dread of making mistakes. The question that he always dreaded.
 frightful: 指使人陷入短暂的惊恐或产生毛骨悚然的感觉。
@@ -1372,6 +1375,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">mplify v. 例证，例示 (This painting exemplifies the artist's early style)
 example n.
@@ -2170,6 +2174,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>desire to spend time together (desire 一般加 to)
 intension n. 紧张；强度，烈度；加强，加剧 
@@ -2265,12 +2270,6 @@
 molecule 分子
 nucleus 原子核
 ion 离子</t>
-  </si>
-  <si>
-    <t>notion 观点，想法，主张
-proposition n.主张，观点；（商业或政治的）提议，建议；法律修正案；欲做的事；（数学或逻辑）命题；v.向某人提议
-  a business proposition 一份商业建议。true proposition / inverse proposition 真命题 /反命题。value proposition 价值主张。
-  This generosity of spirit, this caring about others and about the proposition that we are created equal is the single most effective antidote to the self-centred moral numbness that allows fascism to thrive.</t>
   </si>
   <si>
     <t>myth n.神话，虚构的人或事；荒诞的说法，错误的观点。That myth that you only use 10% of your brain.
@@ -3144,15 +3143,6 @@
     <t>勇敢的</t>
   </si>
   <si>
-    <t>brave 勇敢的
-valiant n.勇敢的人 adj.勇敢的。You have valiantly defied that intimidation. 勇敢地反抗胁迫。
-  vallain n.坏人，恶棍
-valiant ,brave,bold 三者的区别。
-valiant：很强的一个形容词，不必加very在前，意思是很勇敢，通常是文学书籍才看得到这字，平时说话很少人用。
-brave:就勇敢，时常用的，没什么限制。
-bold:大胆自信的，用于形容人或举止</t>
-  </si>
-  <si>
     <t>timid adj 胆怯的，害羞的，犹豫不决的，瞻前顾后的。</t>
   </si>
   <si>
@@ -3202,15 +3192,6 @@
 remit v.宽恕，免除，赦免，缓和，减轻。
 amnesty n.大赦
 </t>
-  </si>
-  <si>
-    <t>treadmill n. 无聊的重复性工作；踏步机，跑步机。(Having kids seems like an endless treadmill of feeding, washing)
-tread n. 梯级；脚步声；轮胎花纹 v. 踩，踏；行走 (trod, trodden/trod) (tread on ones toes 得罪)
-mill n. 磨坊, 工厂, 磨粉机, 面粉厂
-dull adj. 乏味的；阴沉的，钝的 (Life in a small town could be deadly dull.) = blunt。  dull routine 乏味的例行公事。
-boredom n.厌烦，无聊
-fatigue n.疲乏，厌倦；(金属部件的)疲劳，工作服。v.使疲劳，使劳累。adj.疲劳的。弹射器对飞机结构造成的影响就是 fatigue。
-loathe v.讨厌，厌恶</t>
   </si>
   <si>
     <t>urban adj. 城镇的，都市的；住在都市的
@@ -5391,6 +5372,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>tangential adj.</t>
     </r>
@@ -5408,6 +5390,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>tangentially adv.</t>
     </r>
@@ -5924,6 +5907,593 @@
         <charset val="134"/>
       </rPr>
       <t>爆炸，爆破；发出刺耳声；强烈抨击</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">brave </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">勇敢的
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>valiant n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>勇敢的人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> adj.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>勇敢的。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">You have valiantly defied that intimidation. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">勇敢地反抗胁迫。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">  vallain n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>坏人，恶棍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>valiant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：很强的一个形容词，不必加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>very</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">在前，意思是很勇敢，通常是文学书籍才看得到这字，平时说话很少人用。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>brave:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">就勇敢，时常用的，没什么限制。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>bold:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大胆自信的，用于形容人或举止</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">treadmill n. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无聊的重复性工作；踏步机，跑步机。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">(Having kids seems like an endless treadmill of feeding, washing)
+tread n. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>梯级；脚步声；轮胎花纹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> v. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>踩，踏；行走</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> (trod, trodden/trod) (tread on ones toes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>得罪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">)
+mill n. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>磨坊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>工厂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>磨粉机</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">面粉厂
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">dull adj. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>乏味的；阴沉的，钝的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> (Life in a small town could be deadly dull.) = blunt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">  dull routine </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">乏味的例行公事。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>boredom n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">厌烦，无聊
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>fatigue n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疲乏，厌倦；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金属部件的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疲劳，工作服。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>v.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使疲劳，使劳累。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>adj.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疲劳的。弹射器对飞机结构造成的影响就是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> fatigue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>loathe v.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>讨厌，厌恶</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">notion </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">观点，想法，主张
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>proposition n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>主张，观点；（商业或政治的）提议，建议；法律修正案；欲做的事；（数学或逻辑）命题；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>v.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">向某人提议
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">  a business proposition </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一份商业建议。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">true proposition / inverse proposition </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>真命题</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>反命题。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">value proposition </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">价值主张。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">  This generosity of spirit, this caring about others and about the proposition that we are created equal is the single most effective antidote to the self-centred moral numbness that allows fascism to thrive.</t>
     </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -6248,9 +6818,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B456" headerRowCount="0" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B456" headerRowCount="0" headerRowDxfId="3" dataDxfId="2" totalsRowDxfId="1">
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="生词-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6571,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="47" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
@@ -6596,7 +7166,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
@@ -7902,12 +8472,12 @@
       <c r="R57" s="4"/>
       <c r="S57" s="4"/>
     </row>
-    <row r="58" spans="1:19" ht="219.5">
+    <row r="58" spans="1:19" ht="207">
       <c r="A58" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B58" s="46" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
@@ -8393,7 +8963,7 @@
         <v>124</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D79" s="13"/>
       <c r="E79" s="13"/>
@@ -10939,7 +11509,7 @@
       <c r="R189" s="13"/>
       <c r="S189" s="13"/>
     </row>
-    <row r="190" spans="1:19" ht="62.5">
+    <row r="190" spans="1:19" ht="50">
       <c r="A190" s="17"/>
       <c r="B190" s="16" t="s">
         <v>297</v>
@@ -11363,10 +11933,10 @@
       <c r="R208" s="9"/>
       <c r="S208" s="9"/>
     </row>
-    <row r="209" spans="1:19" ht="75">
+    <row r="209" spans="1:19" ht="77">
       <c r="A209" s="12"/>
-      <c r="B209" s="15" t="s">
-        <v>319</v>
+      <c r="B209" s="30" t="s">
+        <v>726</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
@@ -11388,7 +11958,7 @@
     <row r="210" spans="1:19" ht="37.5">
       <c r="A210" s="10"/>
       <c r="B210" s="16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D210" s="9"/>
       <c r="E210" s="9"/>
@@ -11409,10 +11979,10 @@
     </row>
     <row r="211" spans="1:19" ht="137.5">
       <c r="A211" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B211" s="15" t="s">
         <v>321</v>
-      </c>
-      <c r="B211" s="15" t="s">
-        <v>322</v>
       </c>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
@@ -11433,10 +12003,10 @@
     </row>
     <row r="212" spans="1:19" ht="37.5">
       <c r="A212" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B212" s="16" t="s">
         <v>323</v>
-      </c>
-      <c r="B212" s="16" t="s">
-        <v>324</v>
       </c>
       <c r="D212" s="9"/>
       <c r="E212" s="9"/>
@@ -11457,10 +12027,10 @@
     </row>
     <row r="213" spans="1:19">
       <c r="A213" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B213" s="15" t="s">
         <v>325</v>
-      </c>
-      <c r="B213" s="15" t="s">
-        <v>326</v>
       </c>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
@@ -11482,7 +12052,7 @@
     <row r="214" spans="1:19" ht="75">
       <c r="A214" s="8"/>
       <c r="B214" s="16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D214" s="9"/>
       <c r="E214" s="9"/>
@@ -11504,7 +12074,7 @@
     <row r="215" spans="1:19" ht="100">
       <c r="A215" s="12"/>
       <c r="B215" s="35" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
@@ -11525,10 +12095,10 @@
     </row>
     <row r="216" spans="1:19">
       <c r="A216" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="B216" s="16" t="s">
         <v>329</v>
-      </c>
-      <c r="B216" s="16" t="s">
-        <v>330</v>
       </c>
       <c r="D216" s="9"/>
       <c r="E216" s="9"/>
@@ -11550,7 +12120,7 @@
     <row r="217" spans="1:19" ht="37.5">
       <c r="A217" s="12"/>
       <c r="B217" s="15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
@@ -11571,10 +12141,10 @@
     </row>
     <row r="218" spans="1:19" ht="150">
       <c r="A218" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B218" s="16" t="s">
         <v>332</v>
-      </c>
-      <c r="B218" s="16" t="s">
-        <v>333</v>
       </c>
       <c r="D218" s="9"/>
       <c r="E218" s="9"/>
@@ -11596,7 +12166,7 @@
     <row r="219" spans="1:19" ht="75">
       <c r="A219" s="3"/>
       <c r="B219" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
@@ -11617,10 +12187,10 @@
     </row>
     <row r="220" spans="1:19" ht="87.5">
       <c r="A220" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="B220" s="16" t="s">
         <v>335</v>
-      </c>
-      <c r="B220" s="16" t="s">
-        <v>336</v>
       </c>
       <c r="D220" s="9"/>
       <c r="E220" s="9"/>
@@ -11641,10 +12211,10 @@
     </row>
     <row r="221" spans="1:19" ht="50">
       <c r="A221" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B221" s="15" t="s">
         <v>337</v>
-      </c>
-      <c r="B221" s="15" t="s">
-        <v>338</v>
       </c>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
@@ -11666,7 +12236,7 @@
     <row r="222" spans="1:19">
       <c r="A222" s="8"/>
       <c r="B222" s="16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D222" s="9"/>
       <c r="E222" s="9"/>
@@ -11687,10 +12257,10 @@
     </row>
     <row r="223" spans="1:19" ht="150">
       <c r="A223" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B223" s="15" t="s">
         <v>340</v>
-      </c>
-      <c r="B223" s="15" t="s">
-        <v>341</v>
       </c>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
@@ -11711,10 +12281,10 @@
     </row>
     <row r="224" spans="1:19" ht="25">
       <c r="A224" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B224" s="16" t="s">
         <v>342</v>
-      </c>
-      <c r="B224" s="16" t="s">
-        <v>343</v>
       </c>
       <c r="D224" s="9"/>
       <c r="E224" s="9"/>
@@ -11735,10 +12305,10 @@
     </row>
     <row r="225" spans="1:19" ht="112.5">
       <c r="A225" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B225" s="15" t="s">
         <v>344</v>
-      </c>
-      <c r="B225" s="15" t="s">
-        <v>345</v>
       </c>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
@@ -11759,10 +12329,10 @@
     </row>
     <row r="226" spans="1:19" ht="87.5">
       <c r="A226" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="B226" s="16" t="s">
         <v>346</v>
-      </c>
-      <c r="B226" s="16" t="s">
-        <v>347</v>
       </c>
       <c r="D226" s="9"/>
       <c r="E226" s="9"/>
@@ -11783,10 +12353,10 @@
     </row>
     <row r="227" spans="1:19" ht="75">
       <c r="A227" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B227" s="15" t="s">
         <v>348</v>
-      </c>
-      <c r="B227" s="15" t="s">
-        <v>349</v>
       </c>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
@@ -11807,10 +12377,10 @@
     </row>
     <row r="228" spans="1:19" ht="150">
       <c r="A228" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="B228" s="16" t="s">
         <v>350</v>
-      </c>
-      <c r="B228" s="16" t="s">
-        <v>351</v>
       </c>
       <c r="D228" s="9"/>
       <c r="E228" s="9"/>
@@ -11832,7 +12402,7 @@
     <row r="229" spans="1:19">
       <c r="A229" s="36"/>
       <c r="B229" s="15" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
@@ -11854,7 +12424,7 @@
     <row r="230" spans="1:19">
       <c r="A230" s="10"/>
       <c r="B230" s="16" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D230" s="9"/>
       <c r="E230" s="9"/>
@@ -11876,7 +12446,7 @@
     <row r="231" spans="1:19" ht="25">
       <c r="A231" s="12"/>
       <c r="B231" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
@@ -11898,7 +12468,7 @@
     <row r="232" spans="1:19">
       <c r="A232" s="10"/>
       <c r="B232" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D232" s="9"/>
       <c r="E232" s="9"/>
@@ -11920,7 +12490,7 @@
     <row r="233" spans="1:19" ht="50">
       <c r="A233" s="12"/>
       <c r="B233" s="15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
@@ -11942,7 +12512,7 @@
     <row r="234" spans="1:19" ht="37.5">
       <c r="A234" s="10"/>
       <c r="B234" s="16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D234" s="9"/>
       <c r="E234" s="9"/>
@@ -11963,10 +12533,10 @@
     </row>
     <row r="235" spans="1:19" ht="100">
       <c r="A235" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B235" s="15" t="s">
         <v>358</v>
-      </c>
-      <c r="B235" s="15" t="s">
-        <v>359</v>
       </c>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
@@ -11987,10 +12557,10 @@
     </row>
     <row r="236" spans="1:19" ht="50">
       <c r="A236" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B236" s="16" t="s">
         <v>360</v>
-      </c>
-      <c r="B236" s="16" t="s">
-        <v>361</v>
       </c>
       <c r="D236" s="9"/>
       <c r="E236" s="9"/>
@@ -12012,7 +12582,7 @@
     <row r="237" spans="1:19">
       <c r="A237" s="12"/>
       <c r="B237" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
@@ -12034,7 +12604,7 @@
     <row r="238" spans="1:19" ht="25">
       <c r="A238" s="10"/>
       <c r="B238" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D238" s="9"/>
       <c r="E238" s="9"/>
@@ -12056,7 +12626,7 @@
     <row r="239" spans="1:19" ht="87.5">
       <c r="A239" s="12"/>
       <c r="B239" s="15" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
@@ -12078,7 +12648,7 @@
     <row r="240" spans="1:19" ht="112.5">
       <c r="A240" s="17"/>
       <c r="B240" s="16" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D240" s="14"/>
       <c r="E240" s="14"/>
@@ -12099,10 +12669,10 @@
     </row>
     <row r="241" spans="1:19" ht="175">
       <c r="A241" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B241" s="15" t="s">
         <v>366</v>
-      </c>
-      <c r="B241" s="15" t="s">
-        <v>367</v>
       </c>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
@@ -12124,7 +12694,7 @@
     <row r="242" spans="1:19">
       <c r="A242" s="10"/>
       <c r="B242" s="16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D242" s="9"/>
       <c r="E242" s="9"/>
@@ -12146,7 +12716,7 @@
     <row r="243" spans="1:19" ht="37.5">
       <c r="A243" s="12"/>
       <c r="B243" s="15" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
@@ -12168,7 +12738,7 @@
     <row r="244" spans="1:19" ht="75">
       <c r="A244" s="10"/>
       <c r="B244" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D244" s="9"/>
       <c r="E244" s="9"/>
@@ -12189,10 +12759,10 @@
     </row>
     <row r="245" spans="1:19" ht="87.5">
       <c r="A245" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B245" s="15" t="s">
         <v>371</v>
-      </c>
-      <c r="B245" s="15" t="s">
-        <v>372</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
@@ -12214,7 +12784,7 @@
     <row r="246" spans="1:19" ht="62.5">
       <c r="A246" s="8"/>
       <c r="B246" s="16" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D246" s="9"/>
       <c r="E246" s="9"/>
@@ -12235,10 +12805,10 @@
     </row>
     <row r="247" spans="1:19" ht="225">
       <c r="A247" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B247" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="B247" s="15" t="s">
-        <v>375</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
@@ -12259,10 +12829,10 @@
     </row>
     <row r="248" spans="1:19" ht="87.5">
       <c r="A248" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B248" s="16" t="s">
         <v>376</v>
-      </c>
-      <c r="B248" s="16" t="s">
-        <v>377</v>
       </c>
       <c r="D248" s="9"/>
       <c r="E248" s="9"/>
@@ -12283,10 +12853,10 @@
     </row>
     <row r="249" spans="1:19">
       <c r="A249" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B249" s="15" t="s">
         <v>378</v>
-      </c>
-      <c r="B249" s="15" t="s">
-        <v>379</v>
       </c>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
@@ -12308,7 +12878,7 @@
     <row r="250" spans="1:19" ht="87.5">
       <c r="A250" s="10"/>
       <c r="B250" s="16" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D250" s="9"/>
       <c r="E250" s="9"/>
@@ -12330,7 +12900,7 @@
     <row r="251" spans="1:19" ht="112.5">
       <c r="A251" s="3"/>
       <c r="B251" s="15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
@@ -12352,7 +12922,7 @@
     <row r="252" spans="1:19" ht="37.5">
       <c r="A252" s="8"/>
       <c r="B252" s="16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D252" s="9"/>
       <c r="E252" s="9"/>
@@ -12373,10 +12943,10 @@
     </row>
     <row r="253" spans="1:19" ht="75">
       <c r="A253" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B253" s="15" t="s">
         <v>383</v>
-      </c>
-      <c r="B253" s="15" t="s">
-        <v>384</v>
       </c>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
@@ -12398,7 +12968,7 @@
     <row r="254" spans="1:19" ht="37.5">
       <c r="A254" s="10"/>
       <c r="B254" s="16" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D254" s="9"/>
       <c r="E254" s="9"/>
@@ -12420,7 +12990,7 @@
     <row r="255" spans="1:19" ht="25">
       <c r="A255" s="12"/>
       <c r="B255" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
@@ -12442,7 +13012,7 @@
     <row r="256" spans="1:19" ht="25">
       <c r="A256" s="10"/>
       <c r="B256" s="16" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D256" s="9"/>
       <c r="E256" s="9"/>
@@ -12464,7 +13034,7 @@
     <row r="257" spans="1:19" ht="37.5">
       <c r="A257" s="12"/>
       <c r="B257" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
@@ -12486,7 +13056,7 @@
     <row r="258" spans="1:19" ht="50">
       <c r="A258" s="10"/>
       <c r="B258" s="16" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D258" s="9"/>
       <c r="E258" s="9"/>
@@ -12508,7 +13078,7 @@
     <row r="259" spans="1:19" ht="37.5">
       <c r="A259" s="12"/>
       <c r="B259" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
@@ -12530,7 +13100,7 @@
     <row r="260" spans="1:19" ht="37.5">
       <c r="A260" s="10"/>
       <c r="B260" s="16" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D260" s="9"/>
       <c r="E260" s="9"/>
@@ -12552,7 +13122,7 @@
     <row r="261" spans="1:19" ht="25">
       <c r="A261" s="12"/>
       <c r="B261" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
@@ -12574,7 +13144,7 @@
     <row r="262" spans="1:19" ht="25">
       <c r="A262" s="10"/>
       <c r="B262" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D262" s="9"/>
       <c r="E262" s="9"/>
@@ -12596,7 +13166,7 @@
     <row r="263" spans="1:19" ht="125">
       <c r="A263" s="12"/>
       <c r="B263" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
@@ -12618,7 +13188,7 @@
     <row r="264" spans="1:19" ht="37.5">
       <c r="A264" s="10"/>
       <c r="B264" s="16" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D264" s="9"/>
       <c r="E264" s="9"/>
@@ -12660,7 +13230,7 @@
     <row r="266" spans="1:19">
       <c r="A266" s="37"/>
       <c r="B266" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D266" s="9"/>
       <c r="E266" s="9"/>
@@ -12702,7 +13272,7 @@
     <row r="268" spans="1:19">
       <c r="A268" s="10"/>
       <c r="B268" s="16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D268" s="9"/>
       <c r="E268" s="9"/>
@@ -12724,7 +13294,7 @@
     <row r="269" spans="1:19" ht="37.5">
       <c r="A269" s="12"/>
       <c r="B269" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
@@ -12746,7 +13316,7 @@
     <row r="270" spans="1:19" ht="25">
       <c r="A270" s="10"/>
       <c r="B270" s="16" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D270" s="9"/>
       <c r="E270" s="9"/>
@@ -12768,7 +13338,7 @@
     <row r="271" spans="1:19" ht="37.5">
       <c r="A271" s="12"/>
       <c r="B271" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
@@ -12810,7 +13380,7 @@
     <row r="273" spans="1:19" ht="62.5">
       <c r="A273" s="3"/>
       <c r="B273" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
@@ -12852,7 +13422,7 @@
     <row r="275" spans="1:19" ht="25">
       <c r="A275" s="12"/>
       <c r="B275" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
@@ -12873,10 +13443,10 @@
     </row>
     <row r="276" spans="1:19" ht="125">
       <c r="A276" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="B276" s="16" t="s">
         <v>403</v>
-      </c>
-      <c r="B276" s="16" t="s">
-        <v>404</v>
       </c>
       <c r="D276" s="9"/>
       <c r="E276" s="9"/>
@@ -12898,7 +13468,7 @@
     <row r="277" spans="1:19" ht="25">
       <c r="A277" s="12"/>
       <c r="B277" s="15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
@@ -12940,7 +13510,7 @@
     <row r="279" spans="1:19" ht="25">
       <c r="A279" s="12"/>
       <c r="B279" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
@@ -12982,7 +13552,7 @@
     <row r="281" spans="1:19" ht="62.5">
       <c r="A281" s="12"/>
       <c r="B281" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D281" s="4"/>
       <c r="E281" s="4"/>
@@ -13003,10 +13573,10 @@
     </row>
     <row r="282" spans="1:19" ht="87.5">
       <c r="A282" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="B282" s="16" t="s">
         <v>408</v>
-      </c>
-      <c r="B282" s="16" t="s">
-        <v>409</v>
       </c>
       <c r="D282" s="9"/>
       <c r="E282" s="9"/>
@@ -13028,7 +13598,7 @@
     <row r="283" spans="1:19" ht="75">
       <c r="A283" s="12"/>
       <c r="B283" s="15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
@@ -13050,7 +13620,7 @@
     <row r="284" spans="1:19" ht="100">
       <c r="A284" s="10"/>
       <c r="B284" s="16" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D284" s="9"/>
       <c r="E284" s="9"/>
@@ -13072,7 +13642,7 @@
     <row r="285" spans="1:19">
       <c r="A285" s="12"/>
       <c r="B285" s="15" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
@@ -13094,7 +13664,7 @@
     <row r="286" spans="1:19">
       <c r="A286" s="10"/>
       <c r="B286" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D286" s="9"/>
       <c r="E286" s="9"/>
@@ -13115,10 +13685,10 @@
     </row>
     <row r="287" spans="1:19" ht="25">
       <c r="A287" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B287" s="15" t="s">
         <v>414</v>
-      </c>
-      <c r="B287" s="15" t="s">
-        <v>415</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
@@ -13139,10 +13709,10 @@
     </row>
     <row r="288" spans="1:19" ht="100">
       <c r="A288" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="B288" s="16" t="s">
         <v>416</v>
-      </c>
-      <c r="B288" s="16" t="s">
-        <v>417</v>
       </c>
       <c r="D288" s="9"/>
       <c r="E288" s="9"/>
@@ -13164,7 +13734,7 @@
     <row r="289" spans="1:19" ht="25">
       <c r="A289" s="12"/>
       <c r="B289" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
@@ -13186,7 +13756,7 @@
     <row r="290" spans="1:19" ht="87.5">
       <c r="A290" s="10"/>
       <c r="B290" s="16" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D290" s="9"/>
       <c r="E290" s="9"/>
@@ -13207,10 +13777,10 @@
     </row>
     <row r="291" spans="1:19" ht="50">
       <c r="A291" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B291" s="15" t="s">
         <v>420</v>
-      </c>
-      <c r="B291" s="15" t="s">
-        <v>421</v>
       </c>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
@@ -13231,10 +13801,10 @@
     </row>
     <row r="292" spans="1:19" ht="37.5">
       <c r="A292" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B292" s="16" t="s">
         <v>422</v>
-      </c>
-      <c r="B292" s="16" t="s">
-        <v>423</v>
       </c>
       <c r="D292" s="9"/>
       <c r="E292" s="9"/>
@@ -13255,10 +13825,10 @@
     </row>
     <row r="293" spans="1:19" ht="25">
       <c r="A293" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B293" s="15" t="s">
         <v>424</v>
-      </c>
-      <c r="B293" s="15" t="s">
-        <v>425</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
@@ -13279,10 +13849,10 @@
     </row>
     <row r="294" spans="1:19" ht="75">
       <c r="A294" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B294" s="16" t="s">
         <v>426</v>
-      </c>
-      <c r="B294" s="16" t="s">
-        <v>427</v>
       </c>
       <c r="D294" s="9"/>
       <c r="E294" s="9"/>
@@ -13304,7 +13874,7 @@
     <row r="295" spans="1:19" ht="75">
       <c r="A295" s="12"/>
       <c r="B295" s="15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D295" s="4"/>
       <c r="E295" s="4"/>
@@ -13326,7 +13896,7 @@
     <row r="296" spans="1:19" ht="50">
       <c r="A296" s="10"/>
       <c r="B296" s="16" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D296" s="9"/>
       <c r="E296" s="9"/>
@@ -13348,7 +13918,7 @@
     <row r="297" spans="1:19" ht="37.5">
       <c r="A297" s="12"/>
       <c r="B297" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
@@ -13369,10 +13939,10 @@
     </row>
     <row r="298" spans="1:19" ht="100">
       <c r="A298" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="B298" s="16" t="s">
         <v>431</v>
-      </c>
-      <c r="B298" s="16" t="s">
-        <v>432</v>
       </c>
       <c r="D298" s="9"/>
       <c r="E298" s="9"/>
@@ -13393,10 +13963,10 @@
     </row>
     <row r="299" spans="1:19" ht="25">
       <c r="A299" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B299" s="15" t="s">
         <v>433</v>
-      </c>
-      <c r="B299" s="15" t="s">
-        <v>434</v>
       </c>
       <c r="D299" s="4"/>
       <c r="E299" s="4"/>
@@ -13418,7 +13988,7 @@
     <row r="300" spans="1:19">
       <c r="A300" s="8"/>
       <c r="B300" s="16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D300" s="9"/>
       <c r="E300" s="9"/>
@@ -13439,10 +14009,10 @@
     </row>
     <row r="301" spans="1:19">
       <c r="A301" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B301" s="15" t="s">
         <v>436</v>
-      </c>
-      <c r="B301" s="15" t="s">
-        <v>437</v>
       </c>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
@@ -13463,10 +14033,10 @@
     </row>
     <row r="302" spans="1:19" ht="262.5">
       <c r="A302" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="B302" s="16" t="s">
         <v>438</v>
-      </c>
-      <c r="B302" s="16" t="s">
-        <v>439</v>
       </c>
       <c r="D302" s="9"/>
       <c r="E302" s="9"/>
@@ -13487,10 +14057,10 @@
     </row>
     <row r="303" spans="1:19" ht="125">
       <c r="A303" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B303" s="15" t="s">
         <v>440</v>
-      </c>
-      <c r="B303" s="15" t="s">
-        <v>441</v>
       </c>
       <c r="D303" s="4"/>
       <c r="E303" s="4"/>
@@ -13511,10 +14081,10 @@
     </row>
     <row r="304" spans="1:19" ht="37.5">
       <c r="A304" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="B304" s="16" t="s">
         <v>442</v>
-      </c>
-      <c r="B304" s="16" t="s">
-        <v>443</v>
       </c>
       <c r="D304" s="9"/>
       <c r="E304" s="9"/>
@@ -13535,10 +14105,10 @@
     </row>
     <row r="305" spans="1:19" ht="162.5">
       <c r="A305" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B305" s="15" t="s">
         <v>444</v>
-      </c>
-      <c r="B305" s="15" t="s">
-        <v>445</v>
       </c>
       <c r="D305" s="4"/>
       <c r="E305" s="4"/>
@@ -13560,7 +14130,7 @@
     <row r="306" spans="1:19" ht="125">
       <c r="A306" s="8"/>
       <c r="B306" s="16" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D306" s="9"/>
       <c r="E306" s="9"/>
@@ -13581,10 +14151,10 @@
     </row>
     <row r="307" spans="1:19" ht="375">
       <c r="A307" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B307" s="15" t="s">
         <v>447</v>
-      </c>
-      <c r="B307" s="15" t="s">
-        <v>448</v>
       </c>
       <c r="D307" s="4"/>
       <c r="E307" s="4"/>
@@ -13606,7 +14176,7 @@
     <row r="308" spans="1:19" ht="162.5">
       <c r="A308" s="8"/>
       <c r="B308" s="16" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D308" s="9"/>
       <c r="E308" s="9"/>
@@ -13627,10 +14197,10 @@
     </row>
     <row r="309" spans="1:19" ht="175">
       <c r="A309" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B309" s="15" t="s">
         <v>450</v>
-      </c>
-      <c r="B309" s="15" t="s">
-        <v>451</v>
       </c>
       <c r="D309" s="4"/>
       <c r="E309" s="4"/>
@@ -13651,10 +14221,10 @@
     </row>
     <row r="310" spans="1:19" ht="87.5">
       <c r="A310" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="B310" s="16" t="s">
         <v>452</v>
-      </c>
-      <c r="B310" s="16" t="s">
-        <v>453</v>
       </c>
       <c r="D310" s="9"/>
       <c r="E310" s="9"/>
@@ -13676,7 +14246,7 @@
     <row r="311" spans="1:19" ht="37.5">
       <c r="A311" s="3"/>
       <c r="B311" s="15" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D311" s="4"/>
       <c r="E311" s="4"/>
@@ -13698,7 +14268,7 @@
     <row r="312" spans="1:19" ht="175">
       <c r="A312" s="8"/>
       <c r="B312" s="16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D312" s="9"/>
       <c r="E312" s="9"/>
@@ -13719,10 +14289,10 @@
     </row>
     <row r="313" spans="1:19" ht="62.5">
       <c r="A313" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B313" s="15" t="s">
         <v>456</v>
-      </c>
-      <c r="B313" s="15" t="s">
-        <v>457</v>
       </c>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
@@ -13744,7 +14314,7 @@
     <row r="314" spans="1:19">
       <c r="A314" s="8"/>
       <c r="B314" s="16" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D314" s="9"/>
       <c r="E314" s="9"/>
@@ -13765,10 +14335,10 @@
     </row>
     <row r="315" spans="1:19" ht="150">
       <c r="A315" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B315" s="15" t="s">
         <v>459</v>
-      </c>
-      <c r="B315" s="15" t="s">
-        <v>460</v>
       </c>
       <c r="D315" s="4"/>
       <c r="E315" s="4"/>
@@ -13789,10 +14359,10 @@
     </row>
     <row r="316" spans="1:19" ht="287.5">
       <c r="A316" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="B316" s="16" t="s">
         <v>461</v>
-      </c>
-      <c r="B316" s="16" t="s">
-        <v>462</v>
       </c>
       <c r="D316" s="9"/>
       <c r="E316" s="9"/>
@@ -13813,10 +14383,10 @@
     </row>
     <row r="317" spans="1:19">
       <c r="A317" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B317" s="15" t="s">
         <v>463</v>
-      </c>
-      <c r="B317" s="15" t="s">
-        <v>464</v>
       </c>
       <c r="D317" s="4"/>
       <c r="E317" s="4"/>
@@ -13835,12 +14405,12 @@
       <c r="R317" s="4"/>
       <c r="S317" s="4"/>
     </row>
-    <row r="318" spans="1:19" ht="100">
+    <row r="318" spans="1:19" ht="78">
       <c r="A318" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="B318" s="16" t="s">
-        <v>466</v>
+        <v>464</v>
+      </c>
+      <c r="B318" s="27" t="s">
+        <v>724</v>
       </c>
       <c r="D318" s="9"/>
       <c r="E318" s="9"/>
@@ -13862,7 +14432,7 @@
     <row r="319" spans="1:19">
       <c r="A319" s="3"/>
       <c r="B319" s="15" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D319" s="4"/>
       <c r="E319" s="4"/>
@@ -13883,10 +14453,10 @@
     </row>
     <row r="320" spans="1:19">
       <c r="A320" s="8" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B320" s="16" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D320" s="9"/>
       <c r="E320" s="9"/>
@@ -13907,10 +14477,10 @@
     </row>
     <row r="321" spans="1:19">
       <c r="A321" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B321" s="15" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
@@ -13931,10 +14501,10 @@
     </row>
     <row r="322" spans="1:19" ht="150">
       <c r="A322" s="8" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B322" s="16" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D322" s="9"/>
       <c r="E322" s="9"/>
@@ -13955,10 +14525,10 @@
     </row>
     <row r="323" spans="1:19" ht="62.5">
       <c r="A323" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B323" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D323" s="4"/>
       <c r="E323" s="4"/>
@@ -13979,10 +14549,10 @@
     </row>
     <row r="324" spans="1:19" ht="50">
       <c r="A324" s="8" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B324" s="16" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D324" s="9"/>
       <c r="E324" s="9"/>
@@ -14001,10 +14571,10 @@
       <c r="R324" s="9"/>
       <c r="S324" s="9"/>
     </row>
-    <row r="325" spans="1:19" ht="100">
+    <row r="325" spans="1:19" ht="104">
       <c r="A325" s="12"/>
-      <c r="B325" s="15" t="s">
-        <v>478</v>
+      <c r="B325" s="30" t="s">
+        <v>725</v>
       </c>
       <c r="D325" s="4"/>
       <c r="E325" s="4"/>
@@ -14026,7 +14596,7 @@
     <row r="326" spans="1:19" ht="37.5">
       <c r="A326" s="10"/>
       <c r="B326" s="16" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D326" s="9"/>
       <c r="E326" s="9"/>
@@ -14048,7 +14618,7 @@
     <row r="327" spans="1:19" ht="25">
       <c r="A327" s="12"/>
       <c r="B327" s="15" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
@@ -14070,7 +14640,7 @@
     <row r="328" spans="1:19" ht="25">
       <c r="A328" s="8"/>
       <c r="B328" s="16" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D328" s="9"/>
       <c r="E328" s="9"/>
@@ -14092,7 +14662,7 @@
     <row r="329" spans="1:19" ht="150">
       <c r="A329" s="3"/>
       <c r="B329" s="15" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D329" s="4"/>
       <c r="E329" s="4"/>
@@ -14113,10 +14683,10 @@
     </row>
     <row r="330" spans="1:19" ht="37.5">
       <c r="A330" s="8" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B330" s="16" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D330" s="9"/>
       <c r="E330" s="9"/>
@@ -14158,7 +14728,7 @@
     <row r="332" spans="1:19" ht="25">
       <c r="A332" s="10"/>
       <c r="B332" s="16" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D332" s="9"/>
       <c r="E332" s="9"/>
@@ -14179,10 +14749,10 @@
     </row>
     <row r="333" spans="1:19" ht="137.5">
       <c r="A333" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B333" s="15" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
@@ -14203,10 +14773,10 @@
     </row>
     <row r="334" spans="1:19" ht="87.5">
       <c r="A334" s="8" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B334" s="16" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D334" s="9"/>
       <c r="E334" s="9"/>
@@ -14227,10 +14797,10 @@
     </row>
     <row r="335" spans="1:19" ht="50">
       <c r="A335" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B335" s="15" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
@@ -14251,10 +14821,10 @@
     </row>
     <row r="336" spans="1:19" ht="75">
       <c r="A336" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B336" s="16" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D336" s="9"/>
       <c r="E336" s="9"/>
@@ -14276,7 +14846,7 @@
     <row r="337" spans="1:19" ht="37.5">
       <c r="A337" s="12"/>
       <c r="B337" s="15" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D337" s="4"/>
       <c r="E337" s="4"/>
@@ -14298,7 +14868,7 @@
     <row r="338" spans="1:19" ht="75">
       <c r="A338" s="10"/>
       <c r="B338" s="16" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D338" s="9"/>
       <c r="E338" s="9"/>
@@ -14320,7 +14890,7 @@
     <row r="339" spans="1:19" ht="23">
       <c r="A339" s="12"/>
       <c r="B339" s="34" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D339" s="4"/>
       <c r="E339" s="4"/>
@@ -14342,7 +14912,7 @@
     <row r="340" spans="1:19">
       <c r="A340" s="10"/>
       <c r="B340" s="16" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D340" s="9"/>
       <c r="E340" s="9"/>
@@ -14364,7 +14934,7 @@
     <row r="341" spans="1:19">
       <c r="A341" s="12"/>
       <c r="B341" s="15" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
@@ -14386,7 +14956,7 @@
     <row r="342" spans="1:19" ht="25">
       <c r="A342" s="10"/>
       <c r="B342" s="16" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D342" s="9"/>
       <c r="E342" s="9"/>
@@ -14408,7 +14978,7 @@
     <row r="343" spans="1:19">
       <c r="A343" s="12"/>
       <c r="B343" s="15" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D343" s="4"/>
       <c r="E343" s="4"/>
@@ -14430,7 +15000,7 @@
     <row r="344" spans="1:19" ht="25">
       <c r="A344" s="10"/>
       <c r="B344" s="16" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D344" s="9"/>
       <c r="E344" s="9"/>
@@ -14452,7 +15022,7 @@
     <row r="345" spans="1:19">
       <c r="A345" s="12"/>
       <c r="B345" s="15" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D345" s="4"/>
       <c r="E345" s="4"/>
@@ -14474,7 +15044,7 @@
     <row r="346" spans="1:19" ht="37.5">
       <c r="A346" s="10"/>
       <c r="B346" s="16" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D346" s="9"/>
       <c r="E346" s="9"/>
@@ -14496,7 +15066,7 @@
     <row r="347" spans="1:19">
       <c r="A347" s="12"/>
       <c r="B347" s="15" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
@@ -14518,7 +15088,7 @@
     <row r="348" spans="1:19">
       <c r="A348" s="10"/>
       <c r="B348" s="16" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D348" s="9"/>
       <c r="E348" s="9"/>
@@ -14540,7 +15110,7 @@
     <row r="349" spans="1:19">
       <c r="A349" s="12"/>
       <c r="B349" s="15" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D349" s="4"/>
       <c r="E349" s="4"/>
@@ -14562,7 +15132,7 @@
     <row r="350" spans="1:19" ht="25">
       <c r="A350" s="10"/>
       <c r="B350" s="16" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D350" s="9"/>
       <c r="E350" s="9"/>
@@ -14584,7 +15154,7 @@
     <row r="351" spans="1:19">
       <c r="A351" s="12"/>
       <c r="B351" s="15" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
@@ -14606,7 +15176,7 @@
     <row r="352" spans="1:19">
       <c r="A352" s="10"/>
       <c r="B352" s="16" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D352" s="9"/>
       <c r="E352" s="9"/>
@@ -14628,7 +15198,7 @@
     <row r="353" spans="1:19" ht="25">
       <c r="A353" s="12"/>
       <c r="B353" s="15" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D353" s="4"/>
       <c r="E353" s="4"/>
@@ -14650,7 +15220,7 @@
     <row r="354" spans="1:19">
       <c r="A354" s="10"/>
       <c r="B354" s="16" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D354" s="9"/>
       <c r="E354" s="9"/>
@@ -14672,7 +15242,7 @@
     <row r="355" spans="1:19" ht="25">
       <c r="A355" s="12"/>
       <c r="B355" s="15" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D355" s="4"/>
       <c r="E355" s="4"/>
@@ -14694,7 +15264,7 @@
     <row r="356" spans="1:19">
       <c r="A356" s="10"/>
       <c r="B356" s="16" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D356" s="9"/>
       <c r="E356" s="9"/>
@@ -14716,7 +15286,7 @@
     <row r="357" spans="1:19">
       <c r="A357" s="12"/>
       <c r="B357" s="15" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D357" s="4"/>
       <c r="E357" s="4"/>
@@ -14738,7 +15308,7 @@
     <row r="358" spans="1:19">
       <c r="A358" s="10"/>
       <c r="B358" s="16" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D358" s="9"/>
       <c r="E358" s="9"/>
@@ -14760,7 +15330,7 @@
     <row r="359" spans="1:19" ht="37.5">
       <c r="A359" s="12"/>
       <c r="B359" s="15" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D359" s="4"/>
       <c r="E359" s="4"/>
@@ -14782,7 +15352,7 @@
     <row r="360" spans="1:19">
       <c r="A360" s="10"/>
       <c r="B360" s="16" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D360" s="9"/>
       <c r="E360" s="9"/>
@@ -14804,7 +15374,7 @@
     <row r="361" spans="1:19" ht="37.5">
       <c r="A361" s="12"/>
       <c r="B361" s="15" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D361" s="4"/>
       <c r="E361" s="4"/>
@@ -14826,7 +15396,7 @@
     <row r="362" spans="1:19">
       <c r="A362" s="10"/>
       <c r="B362" s="16" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D362" s="9"/>
       <c r="E362" s="9"/>
@@ -14848,7 +15418,7 @@
     <row r="363" spans="1:19">
       <c r="A363" s="12"/>
       <c r="B363" s="15" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
@@ -14870,7 +15440,7 @@
     <row r="364" spans="1:19">
       <c r="A364" s="10"/>
       <c r="B364" s="16" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D364" s="9"/>
       <c r="E364" s="9"/>
@@ -14892,7 +15462,7 @@
     <row r="365" spans="1:19">
       <c r="A365" s="12"/>
       <c r="B365" s="15" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D365" s="4"/>
       <c r="E365" s="4"/>
@@ -14914,7 +15484,7 @@
     <row r="366" spans="1:19">
       <c r="A366" s="10"/>
       <c r="B366" s="16" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D366" s="9"/>
       <c r="E366" s="9"/>
@@ -14936,7 +15506,7 @@
     <row r="367" spans="1:19">
       <c r="A367" s="12"/>
       <c r="B367" s="15" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
@@ -14958,7 +15528,7 @@
     <row r="368" spans="1:19">
       <c r="A368" s="10"/>
       <c r="B368" s="16" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D368" s="9"/>
       <c r="E368" s="9"/>
@@ -14980,7 +15550,7 @@
     <row r="369" spans="1:19">
       <c r="A369" s="12"/>
       <c r="B369" s="15" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
@@ -15002,7 +15572,7 @@
     <row r="370" spans="1:19">
       <c r="A370" s="10"/>
       <c r="B370" s="16" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D370" s="9"/>
       <c r="E370" s="9"/>
@@ -15024,7 +15594,7 @@
     <row r="371" spans="1:19">
       <c r="A371" s="12"/>
       <c r="B371" s="15" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
@@ -15046,7 +15616,7 @@
     <row r="372" spans="1:19">
       <c r="A372" s="10"/>
       <c r="B372" s="16" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D372" s="9"/>
       <c r="E372" s="9"/>
@@ -15068,7 +15638,7 @@
     <row r="373" spans="1:19">
       <c r="A373" s="12"/>
       <c r="B373" s="15" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
@@ -15090,7 +15660,7 @@
     <row r="374" spans="1:19">
       <c r="A374" s="10"/>
       <c r="B374" s="16" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D374" s="9"/>
       <c r="E374" s="9"/>
@@ -15111,10 +15681,10 @@
     </row>
     <row r="375" spans="1:19" ht="150">
       <c r="A375" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B375" s="15" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
@@ -15136,7 +15706,7 @@
     <row r="376" spans="1:19" ht="50">
       <c r="A376" s="10"/>
       <c r="B376" s="16" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D376" s="9"/>
       <c r="E376" s="9"/>
@@ -15158,7 +15728,7 @@
     <row r="377" spans="1:19" ht="75">
       <c r="A377" s="12"/>
       <c r="B377" s="15" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -15180,7 +15750,7 @@
     <row r="378" spans="1:19">
       <c r="A378" s="10"/>
       <c r="B378" s="16" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D378" s="9"/>
       <c r="E378" s="9"/>
@@ -15201,10 +15771,10 @@
     </row>
     <row r="379" spans="1:19" ht="25">
       <c r="A379" s="3" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B379" s="15" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
@@ -15226,7 +15796,7 @@
     <row r="380" spans="1:19" ht="112.5">
       <c r="A380" s="10"/>
       <c r="B380" s="16" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D380" s="9"/>
       <c r="E380" s="9"/>
@@ -15248,7 +15818,7 @@
     <row r="381" spans="1:19" ht="75">
       <c r="A381" s="12"/>
       <c r="B381" s="15" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
@@ -15270,7 +15840,7 @@
     <row r="382" spans="1:19" ht="25">
       <c r="A382" s="10"/>
       <c r="B382" s="16" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D382" s="9"/>
       <c r="E382" s="9"/>
@@ -15292,7 +15862,7 @@
     <row r="383" spans="1:19" ht="50">
       <c r="A383" s="3"/>
       <c r="B383" s="15" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
@@ -15314,7 +15884,7 @@
     <row r="384" spans="1:19" ht="50">
       <c r="A384" s="10"/>
       <c r="B384" s="16" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D384" s="9"/>
       <c r="E384" s="9"/>
@@ -15336,7 +15906,7 @@
     <row r="385" spans="1:19">
       <c r="A385" s="12"/>
       <c r="B385" s="15" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
@@ -15358,7 +15928,7 @@
     <row r="386" spans="1:19">
       <c r="A386" s="10"/>
       <c r="B386" s="16" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D386" s="9"/>
       <c r="E386" s="9"/>
@@ -15380,7 +15950,7 @@
     <row r="387" spans="1:19">
       <c r="A387" s="12"/>
       <c r="B387" s="15" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
@@ -15402,7 +15972,7 @@
     <row r="388" spans="1:19" ht="25">
       <c r="A388" s="10"/>
       <c r="B388" s="16" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D388" s="9"/>
       <c r="E388" s="9"/>
@@ -15424,7 +15994,7 @@
     <row r="389" spans="1:19" ht="112.5">
       <c r="A389" s="12"/>
       <c r="B389" s="15" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
@@ -15446,7 +16016,7 @@
     <row r="390" spans="1:19">
       <c r="A390" s="10"/>
       <c r="B390" s="16" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D390" s="9"/>
       <c r="E390" s="9"/>
@@ -15468,7 +16038,7 @@
     <row r="391" spans="1:19">
       <c r="A391" s="12"/>
       <c r="B391" s="15" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
@@ -15490,7 +16060,7 @@
     <row r="392" spans="1:19">
       <c r="A392" s="10"/>
       <c r="B392" s="16" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D392" s="9"/>
       <c r="E392" s="9"/>
@@ -15512,7 +16082,7 @@
     <row r="393" spans="1:19">
       <c r="A393" s="12"/>
       <c r="B393" s="15" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D393" s="4"/>
       <c r="E393" s="4"/>
@@ -15533,10 +16103,10 @@
     </row>
     <row r="394" spans="1:19" ht="25">
       <c r="A394" s="8" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B394" s="16" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D394" s="9"/>
       <c r="E394" s="9"/>
@@ -15558,7 +16128,7 @@
     <row r="395" spans="1:19" ht="125">
       <c r="A395" s="12"/>
       <c r="B395" s="15" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -15580,7 +16150,7 @@
     <row r="396" spans="1:19">
       <c r="A396" s="10"/>
       <c r="B396" s="16" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D396" s="9"/>
       <c r="E396" s="9"/>
@@ -15602,7 +16172,7 @@
     <row r="397" spans="1:19">
       <c r="A397" s="12"/>
       <c r="B397" s="15" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -15624,359 +16194,359 @@
     <row r="398" spans="1:19">
       <c r="A398" s="38"/>
       <c r="B398" s="45" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="399" spans="1:19">
       <c r="A399" s="38"/>
       <c r="B399" s="45" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="400" spans="1:19">
       <c r="A400" s="38"/>
       <c r="B400" s="45" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" s="38"/>
       <c r="B401" s="45" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" s="38"/>
       <c r="B402" s="45" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="403" spans="1:2" ht="75">
       <c r="A403" s="38"/>
       <c r="B403" s="45" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="404" spans="1:2" ht="62.5">
       <c r="A404" s="38"/>
       <c r="B404" s="45" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="405" spans="1:2" ht="25">
       <c r="A405" s="38"/>
       <c r="B405" s="45" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" s="39" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B406" s="45" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" s="38"/>
       <c r="B407" s="45" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="50">
       <c r="A408" s="39" t="s">
+        <v>563</v>
+      </c>
+      <c r="B408" s="40" t="s">
         <v>566</v>
-      </c>
-      <c r="B408" s="40" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="409" spans="1:2">
       <c r="A409" s="38"/>
       <c r="B409" s="45" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" s="38"/>
       <c r="B410" s="45" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" s="38"/>
       <c r="B411" s="45" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="412" spans="1:2" ht="25">
       <c r="A412" s="38"/>
       <c r="B412" s="45" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" s="38"/>
       <c r="B413" s="45" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" s="38"/>
       <c r="B414" s="45" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="415" spans="1:2" ht="62.5">
       <c r="A415" s="38"/>
       <c r="B415" s="45" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="416" spans="1:2" ht="37.5">
       <c r="A416" s="39" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B416" s="45" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="417" spans="1:2" ht="37.5">
       <c r="A417" s="38"/>
       <c r="B417" s="45" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="418" spans="1:2" ht="50">
       <c r="A418" s="38"/>
       <c r="B418" s="45" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" s="38"/>
       <c r="B419" s="45" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="420" spans="1:2" ht="37.5">
       <c r="A420" s="38"/>
       <c r="B420" s="45" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="421" spans="1:2" ht="25">
       <c r="A421" s="38"/>
       <c r="B421" s="45" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" s="38"/>
       <c r="B422" s="45" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" s="38"/>
       <c r="B423" s="45" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" s="38"/>
       <c r="B424" s="45" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="425" spans="1:2" ht="25">
       <c r="A425" s="39"/>
       <c r="B425" s="45" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="426" spans="1:2" ht="37.5">
       <c r="A426" s="39"/>
       <c r="B426" s="45" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="427" spans="1:2" ht="212.5">
       <c r="A427" s="38"/>
       <c r="B427" s="45" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" s="39"/>
       <c r="B428" s="45" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="429" spans="1:2" ht="137.5">
       <c r="A429" s="39"/>
       <c r="B429" s="45" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="430" spans="1:2" ht="325">
       <c r="A430" s="39" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B430" s="45" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" s="39"/>
       <c r="B431" s="45" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="432" spans="1:2" ht="150">
       <c r="A432" s="39" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B432" s="45" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="433" spans="1:2" ht="37.5">
       <c r="A433" s="39"/>
       <c r="B433" s="45" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="434" spans="1:2" ht="62.5">
       <c r="A434" s="39" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B434" s="45" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="435" spans="1:2" ht="75">
       <c r="A435" s="39" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B435" s="45" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="436" spans="1:2" ht="187.5">
       <c r="A436" s="38"/>
       <c r="B436" s="45" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="437" spans="1:2" ht="125">
       <c r="A437" s="39" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B437" s="45" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" s="38"/>
       <c r="B438" s="45" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="439" spans="1:2" ht="37.5">
       <c r="A439" s="38"/>
       <c r="B439" s="45" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="440" spans="1:2" ht="50">
       <c r="A440" s="38"/>
       <c r="B440" s="45" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" s="38"/>
       <c r="B441" s="45" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="442" spans="1:2" ht="25">
       <c r="A442" s="38"/>
       <c r="B442" s="45" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" s="38"/>
       <c r="B443" s="45" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" s="38"/>
       <c r="B444" s="45" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="445" spans="1:2" ht="150">
       <c r="A445" s="38"/>
       <c r="B445" s="45" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="446" spans="1:2" ht="62.5">
       <c r="A446" s="38"/>
       <c r="B446" s="45" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="447" spans="1:2" ht="75">
       <c r="A447" s="39" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B447" s="45" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="448" spans="1:2" ht="162.5">
       <c r="A448" s="39"/>
       <c r="B448" s="45" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="449" spans="1:19" ht="87.5">
       <c r="A449" s="38"/>
       <c r="B449" s="45" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="450" spans="1:19" ht="112.5">
       <c r="A450" s="38"/>
       <c r="B450" s="45" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="451" spans="1:19">
       <c r="A451" s="39"/>
       <c r="B451" s="45" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="452" spans="1:19" ht="287.5">
       <c r="A452" s="39" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B452" s="45" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="453" spans="1:19" ht="112.5">
       <c r="A453" s="41" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B453" s="45" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D453" s="42"/>
       <c r="E453" s="42"/>
@@ -15997,10 +16567,10 @@
     </row>
     <row r="454" spans="1:19" ht="87.5">
       <c r="A454" s="41" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B454" s="45" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D454" s="43"/>
       <c r="E454" s="43"/>
@@ -16021,32 +16591,32 @@
     </row>
     <row r="455" spans="1:19" ht="112.5">
       <c r="A455" s="39" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B455" s="45" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="456" spans="1:19" ht="25">
       <c r="A456" s="41" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B456" s="45" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="457" spans="1:19" ht="112.5">
       <c r="A457" s="39" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B457" s="45" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="458" spans="1:19" ht="62.5">
       <c r="A458" s="38"/>
       <c r="B458" s="45" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="459" spans="1:19">
@@ -16056,315 +16626,315 @@
     <row r="460" spans="1:19" ht="25">
       <c r="A460" s="38"/>
       <c r="B460" s="45" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="461" spans="1:19" ht="112.5">
       <c r="A461" s="38"/>
       <c r="B461" s="45" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="462" spans="1:19">
       <c r="A462" s="38"/>
       <c r="B462" s="45" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="463" spans="1:19" ht="100">
       <c r="A463" s="39"/>
       <c r="B463" s="45" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="464" spans="1:19" ht="225">
       <c r="A464" s="39"/>
       <c r="B464" s="45" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="465" spans="1:2">
       <c r="A465" s="38"/>
       <c r="B465" s="45" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="466" spans="1:2" ht="25">
       <c r="A466" s="38"/>
       <c r="B466" s="45" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="467" spans="1:2" ht="62.5">
       <c r="A467" s="38"/>
       <c r="B467" s="45" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="468" spans="1:2" ht="150">
       <c r="A468" s="39"/>
       <c r="B468" s="45" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="469" spans="1:2" ht="25">
       <c r="A469" s="38"/>
       <c r="B469" s="45" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="470" spans="1:2" ht="25">
       <c r="A470" s="38"/>
       <c r="B470" s="45" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="471" spans="1:2" ht="62.5">
       <c r="A471" s="38"/>
       <c r="B471" s="45" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="472" spans="1:2" ht="37.5">
       <c r="A472" s="38"/>
       <c r="B472" s="45" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="473" spans="1:2" ht="50">
       <c r="A473" s="39"/>
       <c r="B473" s="45" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="474" spans="1:2" ht="37.5">
       <c r="A474" s="38"/>
       <c r="B474" s="45" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="475" spans="1:2" ht="37.5">
       <c r="A475" s="38"/>
       <c r="B475" s="45" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="476" spans="1:2" ht="50">
       <c r="A476" s="38"/>
       <c r="B476" s="45" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="477" spans="1:2" ht="25">
       <c r="A477" s="38"/>
       <c r="B477" s="45" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="478" spans="1:2" ht="25">
       <c r="A478" s="39"/>
       <c r="B478" s="45" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="479" spans="1:2" ht="75">
       <c r="A479" s="39" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B479" s="45" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" s="38"/>
       <c r="B480" s="45" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="481" spans="1:2" ht="25">
       <c r="A481" s="38"/>
       <c r="B481" s="45" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="482" spans="1:2" ht="75">
       <c r="A482" s="38"/>
       <c r="B482" s="45" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="483" spans="1:2" ht="37.5">
       <c r="A483" s="39" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B483" s="45" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="484" spans="1:2" ht="162.5">
       <c r="A484" s="39" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B484" s="45" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="485" spans="1:2" ht="75">
       <c r="A485" s="38"/>
       <c r="B485" s="45" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="486" spans="1:2" ht="37.5">
       <c r="A486" s="38"/>
       <c r="B486" s="45" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" s="38"/>
       <c r="B487" s="45" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="488" spans="1:2" ht="37.5">
       <c r="A488" s="38"/>
       <c r="B488" s="45" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="489" spans="1:2" ht="37.5">
       <c r="A489" s="38"/>
       <c r="B489" s="45" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="490" spans="1:2" ht="50">
       <c r="A490" s="38"/>
       <c r="B490" s="45" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="491" spans="1:2" ht="25">
       <c r="A491" s="38"/>
       <c r="B491" s="45" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" s="38"/>
       <c r="B492" s="45" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" s="38"/>
       <c r="B493" s="45" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="494" spans="1:2" ht="25">
       <c r="A494" s="38"/>
       <c r="B494" s="45" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" s="38"/>
       <c r="B495" s="45" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="496" spans="1:2" ht="25">
       <c r="A496" s="38"/>
       <c r="B496" s="45" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="497" spans="1:19" ht="25">
       <c r="A497" s="38"/>
       <c r="B497" s="45" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="498" spans="1:19">
       <c r="A498" s="38"/>
       <c r="B498" s="45" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="499" spans="1:19" ht="25">
       <c r="A499" s="38"/>
       <c r="B499" s="45" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="500" spans="1:19" ht="25">
       <c r="A500" s="38"/>
       <c r="B500" s="45" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="501" spans="1:19" ht="25">
       <c r="A501" s="38"/>
       <c r="B501" s="45" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="502" spans="1:19">
       <c r="A502" s="38"/>
       <c r="B502" s="45" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="503" spans="1:19">
       <c r="A503" s="38"/>
       <c r="B503" s="45" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="504" spans="1:19" ht="37.5">
       <c r="A504" s="38"/>
       <c r="B504" s="45" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="505" spans="1:19">
       <c r="A505" s="38"/>
       <c r="B505" s="45" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="506" spans="1:19">
       <c r="A506" s="38"/>
       <c r="B506" s="45" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="507" spans="1:19">
       <c r="A507" s="38"/>
       <c r="B507" s="45" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="508" spans="1:19">
       <c r="A508" s="38"/>
       <c r="B508" s="45" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="509" spans="1:19">
       <c r="A509" s="38"/>
       <c r="B509" s="45" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="510" spans="1:19" ht="137.5">
       <c r="A510" s="41" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B510" s="45" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D510" s="42"/>
       <c r="E510" s="42"/>
@@ -16386,205 +16956,205 @@
     <row r="511" spans="1:19" ht="50">
       <c r="A511" s="38"/>
       <c r="B511" s="45" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="512" spans="1:19" ht="25">
       <c r="A512" s="38"/>
       <c r="B512" s="45" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="513" spans="1:2" ht="25">
       <c r="A513" s="38"/>
       <c r="B513" s="45" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" s="38"/>
       <c r="B514" s="45" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="515" spans="1:2" ht="25">
       <c r="A515" s="38"/>
       <c r="B515" s="45" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="516" spans="1:2" ht="62.5">
       <c r="A516" s="38"/>
       <c r="B516" s="45" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="517" spans="1:2" ht="75">
       <c r="A517" s="38"/>
       <c r="B517" s="45" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="518" spans="1:2" ht="75">
       <c r="A518" s="38"/>
       <c r="B518" s="45" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="519" spans="1:2" ht="112.5">
       <c r="A519" s="38"/>
       <c r="B519" s="45" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="520" spans="1:2" ht="50">
       <c r="A520" s="39" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B520" s="45" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="521" spans="1:2" ht="25">
       <c r="A521" s="38"/>
       <c r="B521" s="45" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" s="38"/>
       <c r="B522" s="45" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" s="38"/>
       <c r="B523" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="524" spans="1:2" ht="187.5">
       <c r="A524" s="38"/>
       <c r="B524" s="45" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="525" spans="1:2" ht="175">
       <c r="A525" s="38"/>
       <c r="B525" s="45" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" s="38"/>
       <c r="B526" s="45" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="527" spans="1:2" ht="275">
       <c r="A527" s="38"/>
       <c r="B527" s="45" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="528" spans="1:2" ht="50">
       <c r="A528" s="38"/>
       <c r="B528" s="45" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="37.5">
       <c r="A529" s="38"/>
       <c r="B529" s="45" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="50">
       <c r="A530" s="38"/>
       <c r="B530" s="45" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="225">
       <c r="A531" s="39" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B531" s="45" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="325">
       <c r="A532" s="39" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B532" s="45" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="237.5">
       <c r="A533" s="39" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B533" s="45" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="200">
       <c r="A534" s="39" t="s">
+        <v>708</v>
+      </c>
+      <c r="B534" s="45" t="s">
         <v>711</v>
-      </c>
-      <c r="B534" s="45" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="50">
       <c r="A535" s="39" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B535" s="45" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="62.5">
       <c r="A536" s="38"/>
       <c r="B536" s="45" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="162.5">
       <c r="A537" s="38"/>
       <c r="B537" s="45" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="37.5">
       <c r="A538" s="38"/>
       <c r="B538" s="45" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="25">
       <c r="A539" s="38"/>
       <c r="B539" s="45" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="25">
       <c r="A540" s="38"/>
       <c r="B540" s="45" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="38"/>
       <c r="B541" s="45" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="542" spans="1:3">
       <c r="A542" s="38"/>
       <c r="B542" s="45" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -20741,8 +21311,9 @@
   <autoFilter ref="A1:S63" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/dict.xlsx
+++ b/dict.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codex\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6926938-B48A-424E-9D80-1CD33C7117D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482611F6-C706-4681-B05A-345CC7340D7B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4432,30 +4432,6 @@
     <t>工程</t>
   </si>
   <si>
-    <t>alternator 交流发电机。
-  the shaft of the alternator is connected to the engine via a belt and pulley 交流发电机的轴通过皮带和皮带轮，与发动机相连。 
-assy n.组件，装配，总成。fan assey 风扇总成。小型的可能也能叫 assembly，比如录相机里的carriage loading assembly 指那个滑架装载机构。
-alternating current 交流电
-rectifier 整流器；改正者，矫正者。
-booster 助推器，推进器，增压器（助力刹车上的助力器）
-modulator 调幅器，调制器（ABS系统中的调制器，精准控制刹车力）
-groove n. 凹槽（如皮带轮上防滑用的）。v.开出沟槽
-bracket n. 托架，支架（如把发电机固定住的）
-housing / case 可以用来描述电机的外壳，plastic outer shell 描述录相带外壳，case用于录相机外壳。
-ignition n.着火，点燃；点火器。
-laminated adj.层压的，层积的，薄板状的；v.分成薄片。laminated sheet 层状薄片，
-  比如电机里面 我们小时候玩的那种圆环片，就是 laminated sheets which have a pattern of slots around the inner edge.
-inverter 逆变器，变频器，将直流变成交流的装置。
-resin n.树脂。Higher power transistors will have a partly metal case(外壳) which attached to a heat sink (散热片，散热器)
-eddy n.涡流，漩涡 v.旋转，起漩涡。eddy current 涡电流，为了防止它的产生，发电机和电动机的电枢要做成多层互相绝缘的金属片。
-armeture n.电枢；盔甲。知识：
-pit n.坑，尘；凹陷，矿井。elevator pit 电梯井
-haul n.v.拖，拉。The truck is good at hauling heavy loads over long distance.
-tow n.v.对车船等的牵引、拖拉，人的牵引、拖带，如拖拉杆箱；牵引绳，拖链。
-cabover 平头卡车，articulated vehicle 铰接式车辆，比如拖头+车厢的卡车（平头或长鼻子都行），与一体式卡车对应。
-hoist v.吊起，提升。n.吊升机械，起重机，吊起。比如天车起重机。</t>
-  </si>
-  <si>
     <t>sheave n.绞缆车 v.捆束。如电梯上的绞缆车，实际上是一个pulley上面缠着钢缆，里面有一些自动刹车等的机械机构。
   shave n.v. 刮(毛)
 winch 绞车，如救援车上安装的绞车
@@ -6494,6 +6470,666 @@
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">  This generosity of spirit, this caring about others and about the proposition that we are created equal is the single most effective antidote to the self-centred moral numbness that allows fascism to thrive.</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">alternator </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">交流发电机。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">  the shaft of the alternator is connected to the engine via a belt and pulley </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>交流发电机的轴通过皮带和皮带轮，与发动机相连。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 
+assy n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>组件，装配，总成。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">fan assey </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>风扇总成。小型的可能也能叫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> assembly</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，比如录相机里的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">carriage loading assembly </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">指那个滑架装载机构。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">alternating current </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">交流电
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">rectifier </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">整流器；改正者，矫正者。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">booster </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">助推器，推进器，增压器（助力刹车上的助力器）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">modulator </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>调幅器，调制器（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ABS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">系统中的调制器，精准控制刹车力）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">groove n. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>凹槽（如皮带轮上防滑用的）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>v.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">开出沟槽
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">bracket n. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">托架，支架（如把发电机固定住的）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">housing / case </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以用来描述电机的外壳，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">plastic outer shell </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>描述录相带外壳，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>case</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">用于录相机外壳。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ignition n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">着火，点燃；点火器。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>laminated adj.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层压的，层积的，薄板状的；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>v.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分成薄片。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">laminated sheet </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">层状薄片，
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比如电机里面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我们小时候玩的那种圆环片，就是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> laminated sheets which have a pattern of slots around the inner edge.
+inverter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">逆变器，变频器，将直流变成交流的装置。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>resin n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>树脂。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>Higher power transistors will have a partly metal case(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外壳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>) which attached to a heat sink (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>散热片，散热器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)
+eddy n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>涡流，漩涡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> v.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>旋转，起漩涡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">eddy current </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">涡电流，为了防止它的产生，发电机和电动机的电枢要做成多层互相绝缘的金属片。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>armeture n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">电枢；盔甲。知识：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>pit n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>坑，尘；凹陷，矿井。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">elevator pit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">电梯井
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>haul n.v.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>拖，拉。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>The truck is good at hauling heavy loads over long distance.
+tow n.v.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">对车船等的牵引、拖拉，人的牵引、拖带，如拖拉杆箱；牵引绳，拖链。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">cabover </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>平头卡车，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">articulated vehicle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>铰接式车辆，比如拖头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">车厢的卡车（平头或长鼻子都行），与一体式卡车对应。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>hoist v.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吊起，提升。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>n.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吊升机械，起重机，吊起。比如天车起重机。</t>
     </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -6614,7 +7250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -6760,6 +7396,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7141,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="47" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
@@ -7166,7 +7805,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
@@ -8477,7 +9116,7 @@
         <v>93</v>
       </c>
       <c r="B58" s="46" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
@@ -8963,7 +9602,7 @@
         <v>124</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D79" s="13"/>
       <c r="E79" s="13"/>
@@ -11936,7 +12575,7 @@
     <row r="209" spans="1:19" ht="77">
       <c r="A209" s="12"/>
       <c r="B209" s="30" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
@@ -14410,7 +15049,7 @@
         <v>464</v>
       </c>
       <c r="B318" s="27" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D318" s="9"/>
       <c r="E318" s="9"/>
@@ -14574,7 +15213,7 @@
     <row r="325" spans="1:19" ht="104">
       <c r="A325" s="12"/>
       <c r="B325" s="30" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D325" s="4"/>
       <c r="E325" s="4"/>
@@ -17083,12 +17722,12 @@
         <v>707</v>
       </c>
     </row>
-    <row r="532" spans="1:3" ht="325">
+    <row r="532" spans="1:3" ht="338">
       <c r="A532" s="39" t="s">
         <v>708</v>
       </c>
-      <c r="B532" s="45" t="s">
-        <v>709</v>
+      <c r="B532" s="49" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="237.5">
@@ -17096,7 +17735,7 @@
         <v>708</v>
       </c>
       <c r="B533" s="45" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="200">
@@ -17104,7 +17743,7 @@
         <v>708</v>
       </c>
       <c r="B534" s="45" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="50">
@@ -17112,49 +17751,49 @@
         <v>708</v>
       </c>
       <c r="B535" s="45" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="62.5">
       <c r="A536" s="38"/>
       <c r="B536" s="45" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="162.5">
       <c r="A537" s="38"/>
       <c r="B537" s="45" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="37.5">
       <c r="A538" s="38"/>
       <c r="B538" s="45" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="25">
       <c r="A539" s="38"/>
       <c r="B539" s="45" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="25">
       <c r="A540" s="38"/>
       <c r="B540" s="45" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="38"/>
       <c r="B541" s="45" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="542" spans="1:3">
       <c r="A542" s="38"/>
       <c r="B542" s="45" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="543" spans="1:3">
